--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G21" s="2"/>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="G22" s="2"/>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="G31" s="2"/>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G36" s="2"/>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2"/>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="2"/>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G43" s="2"/>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="G44" s="2"/>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.12</v>
       </c>
       <c r="G65" s="2"/>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G66" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:13</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
